--- a/public/files/en/one-term-ai-education-plan.xlsx
+++ b/public/files/en/one-term-ai-education-plan.xlsx
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -727,20 +727,6 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Official documents: the Blueprint for Digital Education Development in Primary and Secondary Schools (three-fold leaflet, p.2) requires digital and AI education strategies in school development plans with a clear implementation timetable; the AI Literacy Learning Framework for Primary and Secondary Schools (pp.1-6 to 1-10) sets out cross-subject implementation and progression across four learning stages.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>This file is a teaching resource independently produced by Beets and is not an official EDB document.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
           <t>If you have any comments or questions about this resource, please email enquiry@beets-ai.com</t>
         </is>
       </c>
